--- a/data/cepea-consulta-açucar-santos.reparado.xlsx
+++ b/data/cepea-consulta-açucar-santos.reparado.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filipe.guidastri\Documents\Projetos\painel-controle-commodities\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filipe.guidastri\Documents\Projetos\acompanhamento-cotacao\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{745EDFB7-299C-49E2-8DE1-A1EEFF10BE76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9A447FE1-CF56-4151-8089-2482A261CB09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5760" yWindow="3396" windowWidth="17280" windowHeight="8964"/>
   </bookViews>

--- a/data/cepea-consulta-açucar-santos.reparado.xlsx
+++ b/data/cepea-consulta-açucar-santos.reparado.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filipe.guidastri\Documents\Projetos\acompanhamento-cotacao\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9A447FE1-CF56-4151-8089-2482A261CB09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{41C3112D-BC63-4613-B963-E1F0E77FEA86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5760" yWindow="3396" windowWidth="17280" windowHeight="8964"/>
+    <workbookView xWindow="3240" yWindow="2052" windowWidth="17280" windowHeight="8964"/>
   </bookViews>
   <sheets>
     <sheet name="Plan 1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1221" uniqueCount="1120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1242" uniqueCount="1138">
   <si>
     <t>Açúcar | Indicador Açúcar Cristal - Santos (FOB)</t>
   </si>
@@ -3391,6 +3391,60 @@
   </si>
   <si>
     <t>125,78</t>
+  </si>
+  <si>
+    <t>14/08/2025</t>
+  </si>
+  <si>
+    <t>123,84</t>
+  </si>
+  <si>
+    <t>15/08/2025</t>
+  </si>
+  <si>
+    <t>123,68</t>
+  </si>
+  <si>
+    <t>22,93</t>
+  </si>
+  <si>
+    <t>18/08/2025</t>
+  </si>
+  <si>
+    <t>122,93</t>
+  </si>
+  <si>
+    <t>22,70</t>
+  </si>
+  <si>
+    <t>19/08/2025</t>
+  </si>
+  <si>
+    <t>124,40</t>
+  </si>
+  <si>
+    <t>22,74</t>
+  </si>
+  <si>
+    <t>20/08/2025</t>
+  </si>
+  <si>
+    <t>126,57</t>
+  </si>
+  <si>
+    <t>23,13</t>
+  </si>
+  <si>
+    <t>21/08/2025</t>
+  </si>
+  <si>
+    <t>125,25</t>
+  </si>
+  <si>
+    <t>22/08/2025</t>
+  </si>
+  <si>
+    <t>125,09</t>
   </si>
 </sst>
 </file>
@@ -3842,7 +3896,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J409"/>
+  <dimension ref="A1:J416"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.88671875" customWidth="1"/>
@@ -8344,6 +8398,83 @@
       </c>
       <c r="C409" s="3" t="s">
         <v>750</v>
+      </c>
+    </row>
+    <row r="410" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A410" s="3" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B410" s="3" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C410" s="3" t="s">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="411" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A411" s="3" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B411" s="3" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C411" s="3" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="412" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A412" s="3" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B412" s="3" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C412" s="3" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="413" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A413" s="3" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B413" s="3" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C413" s="3" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="414" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A414" s="3" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B414" s="3" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C414" s="3" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="415" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A415" s="3" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B415" s="3" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C415" s="3" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="416" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A416" s="3" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B416" s="3" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C416" s="3" t="s">
+        <v>985</v>
       </c>
     </row>
   </sheetData>

--- a/data/cepea-consulta-açucar-santos.reparado.xlsx
+++ b/data/cepea-consulta-açucar-santos.reparado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filipe.guidastri\Documents\Projetos\acompanhamento-cotacao\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{41C3112D-BC63-4613-B963-E1F0E77FEA86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{52305C5D-FA98-464E-AEDD-9CE21CA36AEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3240" yWindow="2052" windowWidth="17280" windowHeight="8964"/>
   </bookViews>

--- a/data/cepea-consulta-açucar-santos.reparado.xlsx
+++ b/data/cepea-consulta-açucar-santos.reparado.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filipe.guidastri\Documents\Projetos\acompanhamento-cotacao\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{52305C5D-FA98-464E-AEDD-9CE21CA36AEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{531793C5-473B-40C1-8326-611CB4EE749F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3240" yWindow="2052" windowWidth="17280" windowHeight="8964"/>
+    <workbookView xWindow="5760" yWindow="3396" windowWidth="17280" windowHeight="8964"/>
   </bookViews>
   <sheets>
     <sheet name="Plan 1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1242" uniqueCount="1138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1251" uniqueCount="1147">
   <si>
     <t>Açúcar | Indicador Açúcar Cristal - Santos (FOB)</t>
   </si>
@@ -3445,6 +3445,33 @@
   </si>
   <si>
     <t>125,09</t>
+  </si>
+  <si>
+    <t>25/08/2025</t>
+  </si>
+  <si>
+    <t>124,34</t>
+  </si>
+  <si>
+    <t>22,95</t>
+  </si>
+  <si>
+    <t>26/08/2025</t>
+  </si>
+  <si>
+    <t>124,57</t>
+  </si>
+  <si>
+    <t>22,98</t>
+  </si>
+  <si>
+    <t>27/08/2025</t>
+  </si>
+  <si>
+    <t>125,35</t>
+  </si>
+  <si>
+    <t>23,03</t>
   </si>
 </sst>
 </file>
@@ -3896,7 +3923,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J416"/>
+  <dimension ref="A1:J419"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.88671875" customWidth="1"/>
@@ -8475,6 +8502,39 @@
       </c>
       <c r="C416" s="3" t="s">
         <v>985</v>
+      </c>
+    </row>
+    <row r="417" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A417" s="3" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B417" s="3" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C417" s="3" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="418" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A418" s="3" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B418" s="3" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C418" s="3" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="419" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A419" s="3" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B419" s="3" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C419" s="3" t="s">
+        <v>1146</v>
       </c>
     </row>
   </sheetData>

--- a/data/cepea-consulta-açucar-santos.reparado.xlsx
+++ b/data/cepea-consulta-açucar-santos.reparado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filipe.guidastri\Documents\Projetos\acompanhamento-cotacao\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{531793C5-473B-40C1-8326-611CB4EE749F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{37794287-EE92-4EDA-9253-F8B119F649B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5760" yWindow="3396" windowWidth="17280" windowHeight="8964"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1251" uniqueCount="1147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1254" uniqueCount="1149">
   <si>
     <t>Açúcar | Indicador Açúcar Cristal - Santos (FOB)</t>
   </si>
@@ -3472,6 +3472,12 @@
   </si>
   <si>
     <t>23,03</t>
+  </si>
+  <si>
+    <t>28/08/2025</t>
+  </si>
+  <si>
+    <t>124,46</t>
   </si>
 </sst>
 </file>
@@ -3923,7 +3929,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J419"/>
+  <dimension ref="A1:J420"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.88671875" customWidth="1"/>
@@ -8535,6 +8541,17 @@
       </c>
       <c r="C419" s="3" t="s">
         <v>1146</v>
+      </c>
+    </row>
+    <row r="420" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A420" s="3" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B420" s="3" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C420" s="3" t="s">
+        <v>985</v>
       </c>
     </row>
   </sheetData>
